--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mount.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mount.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="140">
   <si>
     <t>坐骑id</t>
   </si>
@@ -475,9 +475,6 @@
     <t>21600001</t>
   </si>
   <si>
-    <t>200011#6|200021#10</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -493,9 +490,6 @@
     <t>21600002</t>
   </si>
   <si>
-    <t>200011#9|200021#15|207011#666|206011#6</t>
-  </si>
-  <si>
     <t>0#-90#180</t>
   </si>
   <si>
@@ -505,9 +499,6 @@
     <t>炎狼兽</t>
   </si>
   <si>
-    <t>200011#18|200021#30|305012#200</t>
-  </si>
-  <si>
     <t>1#32|2#30|3#31|4#4|5#5|6#6</t>
   </si>
   <si>
@@ -517,9 +508,6 @@
     <t>21600012</t>
   </si>
   <si>
-    <t>200011#18|200021#30|305012#200|325012#500</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -532,9 +520,6 @@
     <t>21600013</t>
   </si>
   <si>
-    <t>200041#40|311012#1200|313012#600</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -547,9 +532,6 @@
     <t>21600006</t>
   </si>
   <si>
-    <t>200041#50|311012#2000|313012#1000</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -559,9 +541,6 @@
     <t>500</t>
   </si>
   <si>
-    <t>200041#20|311012#500</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -574,9 +553,6 @@
     <t>21900002</t>
   </si>
   <si>
-    <t>200041#30|311012#800|313012#300</t>
-  </si>
-  <si>
     <t>-0.5</t>
   </si>
   <si>
@@ -607,51 +583,27 @@
     <t>皇家铠马</t>
   </si>
   <si>
-    <t>207011#1000|305022#200|312112#200</t>
-  </si>
-  <si>
     <t>金龙</t>
   </si>
   <si>
-    <t>200011#30|200021#50|303012#500</t>
-  </si>
-  <si>
     <t>白虎</t>
   </si>
   <si>
-    <t>200011#4|200021#6|207011#66|206011#6</t>
-  </si>
-  <si>
     <t>熊猫</t>
   </si>
   <si>
-    <t>200011#9|200021#15|206011#6|311212#100|319032#300</t>
-  </si>
-  <si>
     <t>星冥龙</t>
   </si>
   <si>
-    <t>303012#200|303022#200|303042#200|303062#200</t>
-  </si>
-  <si>
     <t>雪鹿</t>
   </si>
   <si>
-    <t>305012#300|305022#300</t>
-  </si>
-  <si>
     <t>白毛狮王</t>
   </si>
   <si>
-    <t>303012#300|303022#300</t>
-  </si>
-  <si>
     <t>冥焰马</t>
   </si>
   <si>
-    <t>304012#300|304022#300</t>
-  </si>
-  <si>
     <t>草泥马</t>
   </si>
   <si>
@@ -673,55 +625,28 @@
     <t>绿林狂蝎</t>
   </si>
   <si>
-    <t>305042#500|305062#500</t>
-  </si>
-  <si>
     <t>冻土冰狼</t>
   </si>
   <si>
-    <t>303042#500|303062#500</t>
-  </si>
-  <si>
     <t>星穹泽风</t>
   </si>
   <si>
-    <t>305042#1000|305062#1000</t>
-  </si>
-  <si>
     <t>灵珀蜗天</t>
   </si>
   <si>
-    <t>303042#1000|303062#1000</t>
-  </si>
-  <si>
     <t>90#-270#180</t>
   </si>
   <si>
     <t>碧霄瑶光</t>
   </si>
   <si>
-    <t>304042#1000|304062#1000</t>
-  </si>
-  <si>
     <t>180#-270#180</t>
   </si>
   <si>
-    <t>200011#18|200021#30|305012#2000</t>
-  </si>
-  <si>
-    <t>200011#18|200021#30|305012#20000</t>
-  </si>
-  <si>
     <t>破坏炎狼兽</t>
   </si>
   <si>
-    <t>200021#80|200011#80|311022#1200</t>
-  </si>
-  <si>
     <t>守护炎狼兽</t>
-  </si>
-  <si>
-    <t>206011#100|311022#1200</t>
   </si>
 </sst>
 </file>
@@ -2306,9 +2231,7 @@
       <c r="F5" s="1">
         <v>500</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="J5" s="1">
         <v>0</v>
       </c>
@@ -2334,13 +2257,13 @@
         <v>79</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T5" s="1">
         <v>2.5</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X5" s="1">
         <v>60001</v>
@@ -2351,16 +2274,16 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:25">
       <c r="A6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="1">
         <v>21600002</v>
@@ -2368,14 +2291,12 @@
       <c r="F6" s="1">
         <v>600</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="G6" s="1"/>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M6" s="1">
         <v>1.4</v>
@@ -2393,16 +2314,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T6" s="1">
         <v>2.5</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X6" s="1">
         <v>60001</v>
@@ -2413,10 +2334,10 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2">
         <v>2</v>
@@ -2430,18 +2351,16 @@
       <c r="F7" s="1">
         <v>500</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="9"/>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>79</v>
@@ -2462,13 +2381,13 @@
         <v>60004</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T7" s="1">
         <v>2.5</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X7" s="1">
         <v>60001</v>
@@ -2482,13 +2401,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E8" s="1">
         <v>21600004</v>
@@ -2496,15 +2415,13 @@
       <c r="F8" s="1">
         <v>800</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="9"/>
       <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
@@ -2526,13 +2443,13 @@
         <v>60004</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T8" s="1">
         <v>2.5</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X8" s="1">
         <v>60001</v>
@@ -2543,16 +2460,16 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E9" s="1">
         <v>21600005</v>
@@ -2560,14 +2477,12 @@
       <c r="F9" s="1">
         <v>1000</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="G9" s="1"/>
       <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>79</v>
@@ -2588,13 +2503,13 @@
         <v>13</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T9" s="1">
         <v>2.5</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X9" s="1">
         <v>60001</v>
@@ -2605,32 +2520,30 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <v>1000</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="G10" s="1"/>
       <c r="H10" s="9"/>
       <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>79</v>
@@ -2651,13 +2564,13 @@
         <v>60004</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T10" s="1">
         <v>2.5</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X10" s="1">
         <v>60001</v>
@@ -2668,10 +2581,10 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -2683,16 +2596,14 @@
         <v>21900001</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G11" s="1"/>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>79</v>
@@ -2710,16 +2621,16 @@
         <v>0</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T11" s="1">
         <v>2.5</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X11" s="1">
         <v>60001</v>
@@ -2730,31 +2641,29 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G12" s="1"/>
       <c r="J12" s="1">
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>79</v>
@@ -2763,7 +2672,7 @@
         <v>79</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P12" s="1">
         <v>4.2</v>
@@ -2772,16 +2681,16 @@
         <v>0</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T12" s="1">
         <v>2.5</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X12" s="1">
         <v>60001</v>
@@ -2792,31 +2701,29 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>79</v>
@@ -2825,7 +2732,7 @@
         <v>79</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P13" s="1">
         <v>4.2</v>
@@ -2834,16 +2741,16 @@
         <v>0</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T13" s="1">
         <v>2.5</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X13" s="1">
         <v>60001</v>
@@ -2854,26 +2761,24 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>106</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="J14" s="1">
         <v>0</v>
       </c>
@@ -2896,16 +2801,16 @@
         <v>0</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" s="1">
         <v>2.5</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X14" s="1">
         <v>60001</v>
@@ -2919,7 +2824,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -2933,15 +2838,13 @@
       <c r="F15" s="1">
         <v>600</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>126</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="9"/>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>79</v>
@@ -2962,7 +2865,7 @@
         <v>4</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T15" s="1">
         <v>2.5</v>
@@ -2974,7 +2877,7 @@
         <v>24</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X15" s="1">
         <v>60001</v>
@@ -2988,7 +2891,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -3002,9 +2905,6 @@
       <c r="F16" s="1">
         <v>1300</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
@@ -3036,7 +2936,7 @@
         <v>2.5</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X16" s="1">
         <v>60001</v>
@@ -3050,7 +2950,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C17" s="7">
         <v>3</v>
@@ -3064,9 +2964,6 @@
       <c r="F17" s="1">
         <v>600</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
@@ -3092,13 +2989,13 @@
         <v>114</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T17" s="1">
         <v>2.5</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X17" s="1">
         <v>60001</v>
@@ -3112,7 +3009,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
@@ -3126,9 +3023,7 @@
       <c r="F18" s="1">
         <v>1000</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="G18" s="1"/>
       <c r="J18" s="1">
         <v>0</v>
       </c>
@@ -3154,13 +3049,13 @@
         <v>114</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T18" s="1">
         <v>2.5</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X18" s="1">
         <v>60001</v>
@@ -3174,7 +3069,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -3188,9 +3083,7 @@
       <c r="F19" s="1">
         <v>1500</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="G19" s="1"/>
       <c r="J19" s="1">
         <v>0</v>
       </c>
@@ -3204,7 +3097,7 @@
         <v>24</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P19" s="1">
         <v>3.4</v>
@@ -3222,7 +3115,7 @@
         <v>2.5</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X19" s="1">
         <v>60001</v>
@@ -3236,7 +3129,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -3250,9 +3143,6 @@
       <c r="F20" s="1">
         <v>800</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
@@ -3266,7 +3156,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P20" s="1">
         <v>2.6</v>
@@ -3284,7 +3174,7 @@
         <v>2.5</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X20" s="1">
         <v>60001</v>
@@ -3298,7 +3188,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
@@ -3312,9 +3202,6 @@
       <c r="F21" s="1">
         <v>1200</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="J21" s="1">
         <v>0</v>
       </c>
@@ -3346,7 +3233,7 @@
         <v>2.5</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X21" s="1">
         <v>60001</v>
@@ -3360,7 +3247,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -3374,9 +3261,6 @@
       <c r="F22" s="1">
         <v>800</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="J22" s="1">
         <v>0</v>
       </c>
@@ -3390,7 +3274,7 @@
         <v>30</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="P22" s="1">
         <v>3</v>
@@ -3408,7 +3292,7 @@
         <v>2.5</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X22" s="1">
         <v>60001</v>
@@ -3422,7 +3306,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
@@ -3436,9 +3320,7 @@
       <c r="F23" s="2">
         <v>1200</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G23" s="2"/>
       <c r="J23" s="2">
         <v>0</v>
       </c>
@@ -3470,7 +3352,7 @@
         <v>2.5</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X23" s="1">
         <v>60001</v>
@@ -3484,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -3498,9 +3380,7 @@
       <c r="F24" s="2">
         <v>1200</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G24" s="2"/>
       <c r="J24" s="2">
         <v>0</v>
       </c>
@@ -3533,7 +3413,7 @@
         <v>2.5</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X24" s="1">
         <v>60001</v>
@@ -3547,7 +3427,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
@@ -3561,9 +3441,7 @@
       <c r="F25" s="2">
         <v>1200</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G25" s="2"/>
       <c r="J25" s="2">
         <v>0</v>
       </c>
@@ -3595,7 +3473,7 @@
         <v>2.5</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X25" s="1">
         <v>60001</v>
@@ -3609,7 +3487,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C26" s="1">
         <v>3</v>
@@ -3623,9 +3501,7 @@
       <c r="F26" s="2">
         <v>1200</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G26" s="2"/>
       <c r="J26" s="2">
         <v>0</v>
       </c>
@@ -3658,7 +3534,7 @@
         <v>2.5</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X26" s="1">
         <v>60001</v>
@@ -3672,7 +3548,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C27" s="1">
         <v>3</v>
@@ -3686,9 +3562,7 @@
       <c r="F27" s="2">
         <v>1200</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G27" s="2"/>
       <c r="J27" s="2">
         <v>0</v>
       </c>
@@ -3721,7 +3595,7 @@
         <v>2.5</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X27" s="1">
         <v>60001</v>
@@ -3735,7 +3609,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="C28" s="1">
         <v>3</v>
@@ -3753,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
@@ -3772,10 +3646,10 @@
         <v>0</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T28" s="2">
         <v>2.5</v>
@@ -3787,7 +3661,7 @@
         <v>168</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X28" s="1">
         <v>60001</v>
@@ -3801,7 +3675,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C29" s="2">
         <v>3</v>
@@ -3815,9 +3689,6 @@
       <c r="F29" s="1">
         <v>1000</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J29" s="1">
         <v>0</v>
       </c>
@@ -3849,7 +3720,7 @@
         <v>2.5</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X29" s="1">
         <v>60001</v>
@@ -3863,7 +3734,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C30" s="2">
         <v>3</v>
@@ -3877,9 +3748,6 @@
       <c r="F30" s="1">
         <v>1000</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
@@ -3911,7 +3779,7 @@
         <v>2.5</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X30" s="1">
         <v>60001</v>
@@ -3925,7 +3793,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C31" s="2">
         <v>2</v>
@@ -3939,9 +3807,6 @@
       <c r="F31" s="1">
         <v>1000</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="J31" s="1">
         <v>0</v>
       </c>
@@ -3973,7 +3838,7 @@
         <v>2.5</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X31" s="1">
         <v>60001</v>
@@ -3987,7 +3852,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
@@ -4001,9 +3866,6 @@
       <c r="F32" s="1">
         <v>1200</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="J32" s="1">
         <v>0</v>
       </c>
@@ -4035,7 +3897,7 @@
         <v>2.5</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="X32" s="1">
         <v>60001</v>
@@ -4049,7 +3911,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C33" s="1">
         <v>3</v>
@@ -4063,9 +3925,6 @@
       <c r="F33" s="1">
         <v>1200</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="J33" s="1">
         <v>0</v>
       </c>
@@ -4097,7 +3956,7 @@
         <v>2.5</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="X33" s="1">
         <v>60001</v>
@@ -4111,7 +3970,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" s="2">
         <v>3</v>
@@ -4125,9 +3984,7 @@
       <c r="F34" s="1">
         <v>500</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="9"/>
       <c r="J34" s="1">
         <v>0</v>
@@ -4155,13 +4012,13 @@
         <v>60004</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T34" s="1">
         <v>2.5</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X34" s="1">
         <v>60001</v>
@@ -4175,7 +4032,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C35" s="2">
         <v>3</v>
@@ -4189,9 +4046,7 @@
       <c r="F35" s="1">
         <v>800</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="G35" s="1"/>
       <c r="H35" s="9"/>
       <c r="J35" s="1">
         <v>0</v>
@@ -4219,13 +4074,13 @@
         <v>60004</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T35" s="1">
         <v>2.5</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X35" s="1">
         <v>60001</v>
@@ -4239,7 +4094,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2">
         <v>3</v>
@@ -4253,9 +4108,7 @@
       <c r="F36" s="1">
         <v>800</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>160</v>
-      </c>
+      <c r="G36" s="1"/>
       <c r="H36" s="9"/>
       <c r="J36" s="1">
         <v>0</v>
@@ -4282,13 +4135,13 @@
         <v>60004</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T36" s="1">
         <v>2.5</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X36" s="1">
         <v>60001</v>
@@ -4302,7 +4155,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
@@ -4316,14 +4169,12 @@
       <c r="F37" s="1">
         <v>1000</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>162</v>
-      </c>
+      <c r="G37" s="1"/>
       <c r="J37" s="1">
         <v>0</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>79</v>
@@ -4344,13 +4195,13 @@
         <v>13</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T37" s="1">
         <v>2.5</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X37" s="1">
         <v>60001</v>
@@ -4364,13 +4215,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E38" s="1">
         <v>21600106</v>
@@ -4378,15 +4229,13 @@
       <c r="F38" s="1">
         <v>1000</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="G38" s="1"/>
       <c r="H38" s="9"/>
       <c r="J38" s="1">
         <v>0</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>79</v>
@@ -4407,13 +4256,13 @@
         <v>60004</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T38" s="1">
         <v>2.5</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X38" s="1">
         <v>60001</v>
